--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:16:54+00:00</t>
+    <t>2026-08-26T12:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:41:44+00:00</t>
+    <t>2026-08-26T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:00+00:00</t>
+    <t>2026-08-26T12:57:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:57:55+00:00</t>
+    <t>2026-08-26T13:02:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:02:54+00:00</t>
+    <t>2026-08-26T13:06:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:06:53+00:00</t>
+    <t>2026-08-26T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:20:27+00:00</t>
+    <t>2026-08-26T13:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:28:09+00:00</t>
+    <t>2026-08-26T13:31:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:31:50+00:00</t>
+    <t>2026-08-27T12:43:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:43:51+00:00</t>
+    <t>2026-08-28T07:28:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:28:24+00:00</t>
+    <t>2026-08-28T07:52:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:52:50+00:00</t>
+    <t>2026-08-28T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:32:44+00:00</t>
+    <t>2026-08-28T09:25:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:46:48+00:00</t>
+    <t>2026-08-31T16:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:02:27+00:00</t>
+    <t>2026-08-31T20:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:20:10+00:00</t>
+    <t>2026-08-31T20:24:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:24:53+00:00</t>
+    <t>2026-09-01T08:07:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:07:41+00:00</t>
+    <t>2026-09-01T08:58:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:58:43+00:00</t>
+    <t>2026-09-01T09:49:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:49:43+00:00</t>
+    <t>2026-09-01T09:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:54:08+00:00</t>
+    <t>2026-09-01T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:59:02+00:00</t>
+    <t>2026-09-01T13:10:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:10:54+00:00</t>
+    <t>2026-09-01T13:41:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:41:09+00:00</t>
+    <t>2026-09-03T13:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="583">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:48:05+00:00</t>
+    <t>2026-09-03T16:09:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -896,6 +896,12 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="67875-5"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -5624,7 +5630,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5663,7 +5669,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5684,10 +5690,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5698,10 +5704,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5727,16 +5733,16 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5785,7 +5791,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5806,10 +5812,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5820,10 +5826,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5846,19 +5852,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5907,7 +5913,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5922,19 +5928,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5942,10 +5948,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5968,16 +5974,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6027,7 +6033,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6051,10 +6057,10 @@
         <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6062,14 +6068,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6088,19 +6094,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6149,7 +6155,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6164,19 +6170,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6184,14 +6190,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6210,19 +6216,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6271,7 +6277,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6286,19 +6292,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6306,10 +6312,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6335,13 +6341,13 @@
         <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6391,7 +6397,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6412,13 +6418,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6426,10 +6432,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6452,17 +6458,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6511,7 +6517,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6526,19 +6532,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6546,10 +6552,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6575,16 +6581,16 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6633,7 +6639,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6642,7 +6648,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6651,27 +6657,27 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6786,10 +6792,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6906,10 +6912,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6988,10 +6994,10 @@
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7012,10 +7018,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7026,13 +7032,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
@@ -7095,7 +7101,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7113,7 +7119,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7134,10 +7140,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7148,10 +7154,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7266,10 +7272,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7386,10 +7392,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7415,16 +7421,16 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7434,7 +7440,7 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>82</v>
@@ -7473,7 +7479,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7494,10 +7500,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7508,10 +7514,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7537,13 +7543,13 @@
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7593,7 +7599,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7614,10 +7620,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7628,10 +7634,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7657,14 +7663,14 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7713,7 +7719,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7734,10 +7740,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7748,10 +7754,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7777,14 +7783,14 @@
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7833,7 +7839,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7854,10 +7860,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7868,10 +7874,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7894,19 +7900,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7955,7 +7961,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7976,10 +7982,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7990,13 +7996,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>82</v>
@@ -8059,7 +8065,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8077,7 +8083,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8098,10 +8104,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8112,10 +8118,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8230,10 +8236,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8350,10 +8356,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8379,16 +8385,16 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8398,7 +8404,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8437,7 +8443,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8458,10 +8464,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8472,10 +8478,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8501,13 +8507,13 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8557,7 +8563,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8578,10 +8584,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8592,10 +8598,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8621,14 +8627,14 @@
         <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8677,7 +8683,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8698,10 +8704,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8712,10 +8718,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8741,14 +8747,14 @@
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8797,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8818,10 +8824,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8832,10 +8838,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8858,19 +8864,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8919,7 +8925,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8940,10 +8946,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8954,10 +8960,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8983,16 +8989,16 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9041,7 +9047,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9062,10 +9068,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9076,10 +9082,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9105,16 +9111,16 @@
         <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9142,10 +9148,10 @@
         <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9163,7 +9169,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9172,7 +9178,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9187,7 +9193,7 @@
         <v>192</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9198,14 +9204,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9227,16 +9233,16 @@
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9264,10 +9270,10 @@
         <v>151</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9285,7 +9291,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9303,27 +9309,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9346,19 +9352,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9407,7 +9413,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9428,10 +9434,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9442,10 +9448,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9471,13 +9477,13 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9506,10 +9512,10 @@
         <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9527,7 +9533,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9545,27 +9551,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9591,16 +9597,16 @@
         <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9628,10 +9634,10 @@
         <v>159</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9649,7 +9655,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9670,10 +9676,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9684,10 +9690,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9710,16 +9716,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9769,7 +9775,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9787,27 +9793,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9830,16 +9836,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9889,7 +9895,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9907,27 +9913,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9950,19 +9956,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10011,7 +10017,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10023,7 +10029,7 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10032,10 +10038,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10046,10 +10052,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10164,10 +10170,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10284,14 +10290,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10313,10 +10319,10 @@
         <v>114</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>117</v>
@@ -10371,7 +10377,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10406,10 +10412,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10432,13 +10438,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10489,7 +10495,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10498,7 +10504,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10510,10 +10516,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10524,10 +10530,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10550,13 +10556,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10607,7 +10613,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10616,7 +10622,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10628,10 +10634,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10642,10 +10648,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10671,16 +10677,16 @@
         <v>243</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10708,10 +10714,10 @@
         <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10729,7 +10735,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10747,13 +10753,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10764,10 +10770,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10793,16 +10799,16 @@
         <v>243</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10830,10 +10836,10 @@
         <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10851,7 +10857,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10869,13 +10875,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10886,10 +10892,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10912,17 +10918,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10971,7 +10977,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10995,7 +11001,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11006,10 +11012,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11035,10 +11041,10 @@
         <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11089,7 +11095,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11110,10 +11116,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11124,10 +11130,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11150,16 +11156,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11209,7 +11215,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11230,10 +11236,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11244,10 +11250,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11270,16 +11276,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11329,7 +11335,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11350,10 +11356,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11364,10 +11370,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11390,19 +11396,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11451,7 +11457,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11472,10 +11478,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11486,10 +11492,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11604,10 +11610,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11724,14 +11730,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11753,10 +11759,10 @@
         <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>117</v>
@@ -11811,7 +11817,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11846,10 +11852,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11875,13 +11881,13 @@
         <v>243</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>264</v>
@@ -11933,7 +11939,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -11951,7 +11957,7 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>269</v>
@@ -11968,10 +11974,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11994,19 +12000,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12055,7 +12061,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12073,27 +12079,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12119,16 +12125,16 @@
         <v>243</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12156,10 +12162,10 @@
         <v>151</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12177,7 +12183,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12186,7 +12192,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12201,7 +12207,7 @@
         <v>192</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12212,14 +12218,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12241,16 +12247,16 @@
         <v>243</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12278,10 +12284,10 @@
         <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12299,7 +12305,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12317,27 +12323,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12363,16 +12369,16 @@
         <v>83</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12421,7 +12427,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12442,10 +12448,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:09:48+00:00</t>
+    <t>2026-09-04T09:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:46:57+00:00</t>
+    <t>2026-09-04T09:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
+++ b/branches/1.0.0/StructureDefinition-mii-pr-sdd-berufliche-stellung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:58:25+00:00</t>
+    <t>2026-09-08T12:47:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
